--- a/static/Tasas_y_Deuda.xlsx
+++ b/static/Tasas_y_Deuda.xlsx
@@ -10583,9 +10583,6 @@
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="291" fontId="163" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -10632,6 +10629,10 @@
     </xf>
     <xf numFmtId="289" fontId="184" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="290" fontId="184" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3808">
@@ -34189,13 +34190,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.5" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>1</v>
       </c>
     </row>
@@ -34291,16 +34292,23 @@
       <c r="A10" s="6">
         <v>46204</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="6">
         <v>46387</v>
       </c>
       <c r="C10" s="5">
         <v>2.58E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.25" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
+    <row r="11" spans="1:3" s="2" customFormat="1" ht="11.05">
+      <c r="A11" s="26">
+        <v>46388</v>
+      </c>
+      <c r="B11" s="26">
+        <v>46568</v>
+      </c>
+      <c r="C11" s="27">
+        <v>3.6619999999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="15.25" customHeight="1">
       <c r="A12" s="7"/>
@@ -35211,304 +35219,304 @@
     <col min="16093" max="16384" width="11.3046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="9" customFormat="1" ht="25.1" customHeight="1">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:7" s="8" customFormat="1" ht="25.1" customHeight="1">
+      <c r="A1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>44197</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>44245</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1049701.6599999999</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>44228</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>44271</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>980907.98</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>44256</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>44302</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>970699.5</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>44287</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>44334</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>910843.84</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>44317</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>44363</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>872453.59</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>44348</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>44393</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>909699.34</v>
       </c>
-      <c r="G7" s="12"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>44378</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>44426</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>898519.07</v>
       </c>
-      <c r="G8" s="12"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>44409</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>44455</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>972874.76</v>
       </c>
-      <c r="G9" s="12"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>44440</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>44487</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>1200555.97</v>
       </c>
-      <c r="G10" s="12"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A11" s="10">
+      <c r="A11" s="9">
         <v>44470</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>44516</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>1252203.6599999999</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>44501</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>44546</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>1633095.81</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="12.85">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>44531</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>44579</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>9254377.9900000002</v>
       </c>
-      <c r="G13" s="12"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>44562</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>44608</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>1496121.51</v>
       </c>
-      <c r="G14" s="12"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>44593</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>44636</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>1403817.6</v>
       </c>
-      <c r="G15" s="12"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>44621</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>44670</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>1541435.3</v>
       </c>
-      <c r="G16" s="12"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A17" s="10">
+      <c r="A17" s="9">
         <v>44652</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>44698</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>1476771.71</v>
       </c>
-      <c r="G17" s="12"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>44682</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>44728</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>1652402.8</v>
       </c>
-      <c r="G18" s="12"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>44713</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>44760</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>1957556.31</v>
       </c>
-      <c r="G19" s="12"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>44743</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>44790</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <v>3015291.35</v>
       </c>
-      <c r="G20" s="12"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A21" s="10">
+      <c r="A21" s="9">
         <v>44774</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>44820</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>2613388.7999999998</v>
       </c>
-      <c r="G21" s="12"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>44805</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>44852</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>2674546.46</v>
       </c>
-      <c r="G22" s="12"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>44835</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>44881</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>2486449.64</v>
       </c>
-      <c r="G23" s="12"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>44866</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>44911</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <v>2845086.27</v>
       </c>
-      <c r="G24" s="12"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" ht="15.25" customHeight="1">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>44896</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>44943</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>37750817.140000001</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="11"/>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>
@@ -35525,1178 +35533,1178 @@
   <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="14.23046875" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="12.07421875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="14.23046875" style="14"/>
-    <col min="3" max="3" width="13.921875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="14.07421875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="12" style="14" customWidth="1"/>
-    <col min="6" max="6" width="9.765625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="9.23046875" style="14" customWidth="1"/>
-    <col min="8" max="9" width="8.3046875" style="14" customWidth="1"/>
-    <col min="10" max="10" width="9.4609375" style="14" customWidth="1"/>
-    <col min="11" max="12" width="11.15234375" style="14" customWidth="1"/>
-    <col min="13" max="16384" width="14.23046875" style="14"/>
+    <col min="1" max="1" width="12.07421875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="14.23046875" style="13"/>
+    <col min="3" max="3" width="13.921875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="14.07421875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="12" style="13" customWidth="1"/>
+    <col min="6" max="6" width="9.765625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="9.23046875" style="13" customWidth="1"/>
+    <col min="8" max="9" width="8.3046875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="9.4609375" style="13" customWidth="1"/>
+    <col min="11" max="12" width="11.15234375" style="13" customWidth="1"/>
+    <col min="13" max="16384" width="14.23046875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" customHeight="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" spans="1:12" ht="23">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>44197</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="15">
         <v>44245</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="16">
         <v>1049701.6599999999</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="17">
         <v>682</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>181</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="17">
         <v>184</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="17">
         <v>182</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="17">
         <v>184</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="17">
         <v>80</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="17">
         <v>2.3628200000000001</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="16">
         <v>2480256.08</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="16">
         <v>3529957.74</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>44228</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="15">
         <v>44271</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>980907.98</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>656</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>181</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>184</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="17">
         <v>182</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="17">
         <v>184</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="17">
         <v>80</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="17">
         <v>2.3368199999999999</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="16">
         <v>2292205.39</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="16">
         <v>3273113.37</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>44256</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <v>44302</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>970699.5</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>625</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>181</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>184</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="17">
         <v>182</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="17">
         <v>184</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="17">
         <v>80</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="17">
         <v>2.3058200000000002</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="16">
         <v>2238258.3199999998</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="16">
         <v>3208957.82</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>44287</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>44334</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>910843.84</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>593</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>181</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>184</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <v>182</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <v>184</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="17">
         <v>80</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="17">
         <v>2.2738200000000002</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="16">
         <v>2071094.94</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="16">
         <v>2981938.78</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>44317</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>44363</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>872453.59</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>564</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>181</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>184</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <v>182</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="17">
         <v>184</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="17">
         <v>80</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="17">
         <v>2.2448199999999998</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>1958501.27</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="16">
         <v>2830954.86</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>44348</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="15">
         <v>44393</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>909699.34</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>534</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>181</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>184</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <v>182</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <v>184</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="17">
         <v>80</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="17">
         <v>2.21482</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="16">
         <v>2014820.29</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="16">
         <v>2924519.63</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>44378</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="15">
         <v>44426</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>898519.07</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>501</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>181</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>184</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <v>182</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <v>184</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="17">
         <v>80</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="17">
         <v>2.1818200000000001</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="16">
         <v>1960406.88</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="16">
         <v>2858925.95</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>44409</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="15">
         <v>44455</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>972874.76</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>472</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>181</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>184</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <v>182</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <v>184</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="17">
         <v>80</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="17">
         <v>2.1528200000000002</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="16">
         <v>2094424.24</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="16">
         <v>3067299</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>44440</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="15">
         <v>44487</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>1200555.97</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>440</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>181</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>184</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <v>182</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <v>184</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="17">
         <v>80</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="17">
         <v>2.1208200000000001</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="16">
         <v>2546163.11</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="16">
         <v>3746719.08</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>44470</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="15">
         <v>44516</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>1252203.6599999999</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>411</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>181</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <v>184</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <v>182</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <v>184</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="17">
         <v>80</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="17">
         <v>2.0918199999999998</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="16">
         <v>2619384.66</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="16">
         <v>3871588.32</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>44501</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="15">
         <v>44546</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="16">
         <v>1633095.81</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <v>381</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>181</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>184</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <v>182</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <v>184</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="17">
         <v>80</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="17">
         <v>2.06182</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="16">
         <v>3367149.6</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="16">
         <v>5000245.41</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>44531</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="15">
         <v>44579</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="16">
         <v>9254377.9900000002</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <v>348</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <v>181</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <v>184</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="17">
         <v>182</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="17">
         <v>184</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="17">
         <v>80</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="17">
         <v>2.0288200000000001</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="16">
         <v>18775467.149999999</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="16">
         <v>28029845.140000001</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>44562</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="15">
         <v>44608</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="16">
         <v>1496121.51</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <v>319</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <v>181</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>184</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="17">
         <v>182</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="17">
         <v>184</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="17">
         <v>80</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="17">
         <v>1.9998199999999999</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="16">
         <v>2991973.72</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="16">
         <v>4488095.2300000004</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>44593</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="15">
         <v>44636</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="16">
         <v>1403817.6</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <v>291</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>181</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <v>184</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="17">
         <v>182</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="17">
         <v>184</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="17">
         <v>80</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="17">
         <v>1.9718199999999999</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="16">
         <v>2768075.62</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="16">
         <v>4171893.22</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>44621</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="15">
         <v>44670</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="16">
         <v>1541435.3</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>257</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>181</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>184</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="17">
         <v>182</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="17">
         <v>184</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="17">
         <v>80</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="17">
         <v>1.9378200000000001</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="16">
         <v>2987024.15</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="16">
         <v>4528459.45</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>44652</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="15">
         <v>44698</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="16">
         <v>1476771.71</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <v>229</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <v>181</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <v>184</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <v>182</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="17">
         <v>184</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="17">
         <v>80</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="17">
         <v>1.9098200000000001</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="16">
         <v>2820368.15</v>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="16">
         <v>4297139.8600000003</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>44682</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="15">
         <v>44728</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>1652402.8</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <v>199</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>181</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <v>184</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="17">
         <v>182</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="17">
         <v>184</v>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="17">
         <v>80</v>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="17">
         <v>1.87982</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="16">
         <v>3106219.83</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="16">
         <v>4758622.63</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>44713</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <v>44760</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="16">
         <v>1957556.31</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="17">
         <v>167</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <v>181</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <v>184</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="17">
         <v>182</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="17">
         <v>184</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="17">
         <v>80</v>
       </c>
-      <c r="J20" s="18">
+      <c r="J20" s="17">
         <v>1.84782</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="16">
         <v>3617211.7</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="16">
         <v>5574768.0099999998</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>44743</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="15">
         <v>44790</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="16">
         <v>3015291.35</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <v>137</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <v>181</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="17">
         <v>184</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="17">
         <v>182</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="17">
         <v>184</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="17">
         <v>80</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="17">
         <v>1.81782</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="16">
         <v>5481256.9199999999</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="16">
         <v>8496548.2699999996</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>44774</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="15">
         <v>44820</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="16">
         <v>2613388.7999999998</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="17">
         <v>107</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="17">
         <v>181</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="17">
         <v>184</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="17">
         <v>182</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="17">
         <v>184</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="17">
         <v>80</v>
       </c>
-      <c r="J22" s="18">
+      <c r="J22" s="17">
         <v>1.78782</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="16">
         <v>4672268.76</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="16">
         <v>7285657.5599999996</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>44805</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="15">
         <v>44852</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="16">
         <v>2674546.46</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="17">
         <v>75</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="17">
         <v>181</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="17">
         <v>184</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="17">
         <v>182</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="17">
         <v>184</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="17">
         <v>80</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="17">
         <v>1.7558199999999999</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="16">
         <v>4696022.17</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="16">
         <v>7370568.6299999999</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>44835</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="15">
         <v>44881</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="16">
         <v>2486449.64</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="17">
         <v>46</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="17">
         <v>181</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="17">
         <v>184</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="17">
         <v>182</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="17">
         <v>184</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="17">
         <v>80</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="17">
         <v>1.72682</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="16">
         <v>4293650.97</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="16">
         <v>6780100.6100000003</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>44866</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="15">
         <v>44911</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="16">
         <v>2845086.27</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="17">
         <v>16</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="17">
         <v>181</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="17">
         <v>184</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="17">
         <v>182</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="17">
         <v>184</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="17">
         <v>80</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="17">
         <v>1.69682</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="16">
         <v>4827599.28</v>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="16">
         <v>7672685.5499999998</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>44896</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="15">
         <v>44943</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="16">
         <v>37750817.140000001</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="17">
         <v>0</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="17">
         <v>165</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="17">
         <v>184</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="17">
         <v>182</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="17">
         <v>184</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="17">
         <v>80</v>
       </c>
-      <c r="J26" s="18">
+      <c r="J26" s="17">
         <v>1.65084667</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="16">
         <v>62320810.640000001</v>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="16">
         <v>100071627.78</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="13"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23" t="s">
+      <c r="A29" s="12"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
     </row>
     <row r="30" spans="1:12" ht="34.450000000000003">
-      <c r="A30" s="13"/>
-      <c r="B30" s="22" t="s">
+      <c r="A30" s="12"/>
+      <c r="B30" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="13"/>
-      <c r="B31" s="18">
+      <c r="A31" s="12"/>
+      <c r="B31" s="17">
         <v>2021</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="16">
         <v>20905933.170000002</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>44418131.93</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>65324065.100000001</v>
       </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="13"/>
-      <c r="B32" s="18">
+      <c r="A32" s="12"/>
+      <c r="B32" s="17">
         <v>2022</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="16">
         <v>60913684.890000001</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <v>104582481.91</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>165496166.80000001</v>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="13"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="24" t="s">
+      <c r="A34" s="12"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
     </row>
     <row r="35" spans="1:12" ht="34.450000000000003">
-      <c r="A35" s="13"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="22" t="s">
+      <c r="A35" s="12"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="17">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="16">
         <v>81819618.060000002</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="16">
         <v>149000613.84</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="16">
         <v>230820231.90000001</v>
       </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/static/Tasas_y_Deuda.xlsx
+++ b/static/Tasas_y_Deuda.xlsx
@@ -34307,7 +34307,7 @@
         <v>46568</v>
       </c>
       <c r="C11" s="27">
-        <v>3.6619999999999999</v>
+        <v>3.662E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.25" customHeight="1">
